--- a/master-db/chevrolet.xlsx
+++ b/master-db/chevrolet.xlsx
@@ -61,7 +61,7 @@
     <t/>
   </si>
   <si>
-    <t>대기</t>
+    <t>완료</t>
   </si>
   <si>
     <t>15~18년</t>
@@ -346,7 +346,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>대기</t>
+    <t>완료</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>

--- a/master-db/chevrolet.xlsx
+++ b/master-db/chevrolet.xlsx
@@ -1919,7 +1919,7 @@
         <v>66</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="G46" t="s">
         <v>12</v>
